--- a/data_src/xlsx表/关卡表.xlsx
+++ b/data_src/xlsx表/关卡表.xlsx
@@ -703,20 +703,14 @@
           <t>04.30.2022</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>80</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>

--- a/data_src/xlsx表/关卡表.xlsx
+++ b/data_src/xlsx表/关卡表.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,33 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +59,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,614 +453,703 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>levelid</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>chapter_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>scene_path</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>data_dir</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>cheer_reward</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>bgm_id</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>unlockconditionid</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>codex_unlock_id</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>text2</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>grantstars</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>grantfp</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>grantintel</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>grantpostid</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>grantpostcount</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>unlockpostcount</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>关卡唯一ID</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>章节ID</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>章节内排序</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>关卡标题</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Godot场景路径</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>单关配表目录名</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>应援棒奖励（废弃字段，保留兼容）</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>背景音乐ID</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>解锁条件ID</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>图鉴解锁ID</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>动态页时间文案</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>通关给星星</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>通关给饭圈积分</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>通关给情报点</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>通关解锁发帖次数</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>关卡id</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>章节</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>顺序</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>数据目录</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>应援</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>bgm</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>解锁条件</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>图鉴</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>奖励星</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>奖励积分</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>情报(停用)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>赠送帖</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>赠送数</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>解锁帖数</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ch1_l01</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>化妆室疑云</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>res://scenes/idol/ch1_l01.tscn</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>ch1_l01</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>bgm_level_default</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>04.30.2022</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>80</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>3010</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ch1_l02</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>后台走廊</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>res://scenes/idol/idol_level.tscn</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>ch1_l02</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bgm_level_default</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>04.30.2023</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>ch1_l03</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>后台走廊2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>res://scenes/idol/idol_level.tscn</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>ch1_l03</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>bgm_level_default</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>04.30.2024</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ch1_l04</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>后台走廊3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>res://scenes/idol/idol_level.tscn</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>ch1_l04</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>bgm_level_default</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>3001</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>04.30.2025</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>ch1_l05</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>后台走廊4</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>res://scenes/idol/idol_level.tscn</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>ch1_l05</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>bgm_level_default</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>3001</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>04.30.2026</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
